--- a/final_data_pipeline/output/311613_elec_options.xlsx
+++ b/final_data_pipeline/output/311613_elec_options.xlsx
@@ -3569,7 +3569,7 @@
         <v>110</v>
       </c>
       <c r="AD30">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE30">
         <v>8000</v>
@@ -3664,7 +3664,7 @@
         <v>110</v>
       </c>
       <c r="AD31">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE31">
         <v>8000</v>
@@ -3759,7 +3759,7 @@
         <v>110</v>
       </c>
       <c r="AD32">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE32">
         <v>8000</v>
@@ -3854,7 +3854,7 @@
         <v>110</v>
       </c>
       <c r="AD33">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE33">
         <v>8000</v>
@@ -3949,7 +3949,7 @@
         <v>110</v>
       </c>
       <c r="AD34">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE34">
         <v>8000</v>
@@ -4044,7 +4044,7 @@
         <v>110</v>
       </c>
       <c r="AD35">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE35">
         <v>8000</v>
@@ -4139,7 +4139,7 @@
         <v>110</v>
       </c>
       <c r="AD36">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE36">
         <v>8000</v>
@@ -4234,7 +4234,7 @@
         <v>110</v>
       </c>
       <c r="AD37">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE37">
         <v>8000</v>
@@ -4329,7 +4329,7 @@
         <v>110</v>
       </c>
       <c r="AD38">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AE38">
         <v>8000</v>
@@ -4424,7 +4424,7 @@
         <v>110</v>
       </c>
       <c r="AD39">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AE39">
         <v>8000</v>
@@ -4519,7 +4519,7 @@
         <v>110</v>
       </c>
       <c r="AD40">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AE40">
         <v>8000</v>
@@ -4614,7 +4614,7 @@
         <v>110</v>
       </c>
       <c r="AD41">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AE41">
         <v>8000</v>
@@ -4709,7 +4709,7 @@
         <v>110</v>
       </c>
       <c r="AD42">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE42">
         <v>8000</v>
@@ -4804,7 +4804,7 @@
         <v>110</v>
       </c>
       <c r="AD43">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE43">
         <v>8000</v>
@@ -4899,7 +4899,7 @@
         <v>110</v>
       </c>
       <c r="AD44">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE44">
         <v>8000</v>
@@ -4994,7 +4994,7 @@
         <v>110</v>
       </c>
       <c r="AD45">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE45">
         <v>8000</v>
@@ -5089,7 +5089,7 @@
         <v>110</v>
       </c>
       <c r="AD46">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE46">
         <v>8000</v>
@@ -5184,7 +5184,7 @@
         <v>110</v>
       </c>
       <c r="AD47">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE47">
         <v>8000</v>
@@ -5279,7 +5279,7 @@
         <v>110</v>
       </c>
       <c r="AD48">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE48">
         <v>8000</v>
@@ -5374,7 +5374,7 @@
         <v>110</v>
       </c>
       <c r="AD49">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE49">
         <v>8000</v>
@@ -5469,7 +5469,7 @@
         <v>110</v>
       </c>
       <c r="AD50">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE50">
         <v>8000</v>
@@ -5564,7 +5564,7 @@
         <v>110</v>
       </c>
       <c r="AD51">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE51">
         <v>8000</v>
@@ -5659,7 +5659,7 @@
         <v>110</v>
       </c>
       <c r="AD52">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE52">
         <v>8000</v>
@@ -5754,7 +5754,7 @@
         <v>110</v>
       </c>
       <c r="AD53">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE53">
         <v>8000</v>
@@ -5849,7 +5849,7 @@
         <v>110</v>
       </c>
       <c r="AD54">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE54">
         <v>8000</v>
@@ -5944,7 +5944,7 @@
         <v>110</v>
       </c>
       <c r="AD55">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE55">
         <v>8000</v>
@@ -6039,7 +6039,7 @@
         <v>110</v>
       </c>
       <c r="AD56">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE56">
         <v>8000</v>
@@ -6134,7 +6134,7 @@
         <v>110</v>
       </c>
       <c r="AD57">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE57">
         <v>8000</v>
@@ -6229,7 +6229,7 @@
         <v>110</v>
       </c>
       <c r="AD58">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AE58">
         <v>8000</v>
@@ -6324,7 +6324,7 @@
         <v>110</v>
       </c>
       <c r="AD59">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AE59">
         <v>8000</v>
@@ -6419,7 +6419,7 @@
         <v>110</v>
       </c>
       <c r="AD60">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AE60">
         <v>8000</v>
@@ -6514,7 +6514,7 @@
         <v>110</v>
       </c>
       <c r="AD61">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AE61">
         <v>8000</v>
@@ -9269,7 +9269,7 @@
         <v>110</v>
       </c>
       <c r="AD90">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE90">
         <v>8000</v>
@@ -9364,7 +9364,7 @@
         <v>110</v>
       </c>
       <c r="AD91">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE91">
         <v>8000</v>
@@ -9459,7 +9459,7 @@
         <v>110</v>
       </c>
       <c r="AD92">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE92">
         <v>8000</v>
@@ -9554,7 +9554,7 @@
         <v>110</v>
       </c>
       <c r="AD93">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE93">
         <v>8000</v>
@@ -9649,7 +9649,7 @@
         <v>110</v>
       </c>
       <c r="AD94">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE94">
         <v>8000</v>
@@ -9744,7 +9744,7 @@
         <v>110</v>
       </c>
       <c r="AD95">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE95">
         <v>8000</v>
@@ -9839,7 +9839,7 @@
         <v>110</v>
       </c>
       <c r="AD96">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE96">
         <v>8000</v>
@@ -9934,7 +9934,7 @@
         <v>110</v>
       </c>
       <c r="AD97">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE97">
         <v>8000</v>
@@ -10029,7 +10029,7 @@
         <v>110</v>
       </c>
       <c r="AD98">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE98">
         <v>8000</v>
@@ -10124,7 +10124,7 @@
         <v>110</v>
       </c>
       <c r="AD99">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE99">
         <v>8000</v>
@@ -10219,7 +10219,7 @@
         <v>110</v>
       </c>
       <c r="AD100">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE100">
         <v>8000</v>
@@ -10314,7 +10314,7 @@
         <v>110</v>
       </c>
       <c r="AD101">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE101">
         <v>8000</v>
@@ -10409,7 +10409,7 @@
         <v>110</v>
       </c>
       <c r="AD102">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE102">
         <v>8000</v>
@@ -10504,7 +10504,7 @@
         <v>110</v>
       </c>
       <c r="AD103">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE103">
         <v>8000</v>
@@ -10599,7 +10599,7 @@
         <v>110</v>
       </c>
       <c r="AD104">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE104">
         <v>8000</v>
@@ -10694,7 +10694,7 @@
         <v>110</v>
       </c>
       <c r="AD105">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE105">
         <v>8000</v>
@@ -11169,7 +11169,7 @@
         <v>110</v>
       </c>
       <c r="AD110">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE110">
         <v>8000</v>
@@ -11264,7 +11264,7 @@
         <v>110</v>
       </c>
       <c r="AD111">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE111">
         <v>8000</v>
@@ -11359,7 +11359,7 @@
         <v>110</v>
       </c>
       <c r="AD112">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE112">
         <v>8000</v>
@@ -11454,7 +11454,7 @@
         <v>110</v>
       </c>
       <c r="AD113">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE113">
         <v>8000</v>
@@ -11549,7 +11549,7 @@
         <v>110</v>
       </c>
       <c r="AD114">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE114">
         <v>8000</v>
@@ -11644,7 +11644,7 @@
         <v>110</v>
       </c>
       <c r="AD115">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE115">
         <v>8000</v>
@@ -11739,7 +11739,7 @@
         <v>110</v>
       </c>
       <c r="AD116">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE116">
         <v>8000</v>
@@ -11834,7 +11834,7 @@
         <v>110</v>
       </c>
       <c r="AD117">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE117">
         <v>8000</v>
@@ -11929,7 +11929,7 @@
         <v>110</v>
       </c>
       <c r="AD118">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE118">
         <v>8000</v>
@@ -12024,7 +12024,7 @@
         <v>110</v>
       </c>
       <c r="AD119">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE119">
         <v>8000</v>
@@ -12119,7 +12119,7 @@
         <v>110</v>
       </c>
       <c r="AD120">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE120">
         <v>8000</v>
@@ -12214,7 +12214,7 @@
         <v>110</v>
       </c>
       <c r="AD121">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE121">
         <v>8000</v>
@@ -14209,7 +14209,7 @@
         <v>110</v>
       </c>
       <c r="AD142">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE142">
         <v>8000</v>
@@ -14304,7 +14304,7 @@
         <v>110</v>
       </c>
       <c r="AD143">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE143">
         <v>8000</v>
@@ -14399,7 +14399,7 @@
         <v>110</v>
       </c>
       <c r="AD144">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE144">
         <v>8000</v>
@@ -14494,7 +14494,7 @@
         <v>110</v>
       </c>
       <c r="AD145">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE145">
         <v>8000</v>
@@ -14589,7 +14589,7 @@
         <v>110</v>
       </c>
       <c r="AD146">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE146">
         <v>8000</v>
@@ -14684,7 +14684,7 @@
         <v>110</v>
       </c>
       <c r="AD147">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE147">
         <v>8000</v>
@@ -14779,7 +14779,7 @@
         <v>110</v>
       </c>
       <c r="AD148">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE148">
         <v>8000</v>
@@ -14874,7 +14874,7 @@
         <v>110</v>
       </c>
       <c r="AD149">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE149">
         <v>8000</v>
@@ -14969,7 +14969,7 @@
         <v>110</v>
       </c>
       <c r="AD150">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE150">
         <v>8000</v>
@@ -15064,7 +15064,7 @@
         <v>110</v>
       </c>
       <c r="AD151">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE151">
         <v>8000</v>
@@ -15159,7 +15159,7 @@
         <v>110</v>
       </c>
       <c r="AD152">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE152">
         <v>8000</v>
@@ -15254,7 +15254,7 @@
         <v>110</v>
       </c>
       <c r="AD153">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE153">
         <v>8000</v>
@@ -15349,7 +15349,7 @@
         <v>110</v>
       </c>
       <c r="AD154">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE154">
         <v>8000</v>
@@ -15444,7 +15444,7 @@
         <v>110</v>
       </c>
       <c r="AD155">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE155">
         <v>8000</v>
@@ -15539,7 +15539,7 @@
         <v>110</v>
       </c>
       <c r="AD156">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE156">
         <v>8000</v>
@@ -15634,7 +15634,7 @@
         <v>110</v>
       </c>
       <c r="AD157">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AE157">
         <v>8000</v>
@@ -15729,7 +15729,7 @@
         <v>110</v>
       </c>
       <c r="AD158">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE158">
         <v>8000</v>
@@ -15824,7 +15824,7 @@
         <v>110</v>
       </c>
       <c r="AD159">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE159">
         <v>8000</v>
@@ -15919,7 +15919,7 @@
         <v>110</v>
       </c>
       <c r="AD160">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE160">
         <v>8000</v>
@@ -16014,7 +16014,7 @@
         <v>110</v>
       </c>
       <c r="AD161">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE161">
         <v>8000</v>
@@ -16109,7 +16109,7 @@
         <v>110</v>
       </c>
       <c r="AD162">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AE162">
         <v>8000</v>
@@ -16204,7 +16204,7 @@
         <v>110</v>
       </c>
       <c r="AD163">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AE163">
         <v>8000</v>
@@ -16299,7 +16299,7 @@
         <v>110</v>
       </c>
       <c r="AD164">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AE164">
         <v>8000</v>
@@ -16394,7 +16394,7 @@
         <v>110</v>
       </c>
       <c r="AD165">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AE165">
         <v>8000</v>
@@ -16489,7 +16489,7 @@
         <v>110</v>
       </c>
       <c r="AD166">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AE166">
         <v>8000</v>
@@ -16584,7 +16584,7 @@
         <v>110</v>
       </c>
       <c r="AD167">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AE167">
         <v>8000</v>
@@ -16679,7 +16679,7 @@
         <v>110</v>
       </c>
       <c r="AD168">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AE168">
         <v>8000</v>
@@ -16774,7 +16774,7 @@
         <v>110</v>
       </c>
       <c r="AD169">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AE169">
         <v>8000</v>
@@ -17629,7 +17629,7 @@
         <v>110</v>
       </c>
       <c r="AD178">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE178">
         <v>8000</v>
@@ -17724,7 +17724,7 @@
         <v>110</v>
       </c>
       <c r="AD179">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE179">
         <v>8000</v>
@@ -17819,7 +17819,7 @@
         <v>110</v>
       </c>
       <c r="AD180">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE180">
         <v>8000</v>
@@ -17914,7 +17914,7 @@
         <v>110</v>
       </c>
       <c r="AD181">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE181">
         <v>8000</v>
@@ -18009,7 +18009,7 @@
         <v>110</v>
       </c>
       <c r="AD182">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE182">
         <v>8000</v>
@@ -18104,7 +18104,7 @@
         <v>110</v>
       </c>
       <c r="AD183">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE183">
         <v>8000</v>
@@ -18199,7 +18199,7 @@
         <v>110</v>
       </c>
       <c r="AD184">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE184">
         <v>8000</v>
@@ -18294,7 +18294,7 @@
         <v>110</v>
       </c>
       <c r="AD185">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE185">
         <v>8000</v>
